--- a/artfynd/A 18014-2022 artfynd.xlsx
+++ b/artfynd/A 18014-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18014-2022 artfynd.xlsx
+++ b/artfynd/A 18014-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109004914</v>
+        <v>109007881</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577478.1397211257</v>
+        <v>577275</v>
       </c>
       <c r="R2" t="n">
-        <v>7055697.761606915</v>
+        <v>7055743</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -766,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109008153</v>
+        <v>112332579</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,38 +794,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Meåforsbodarna, Ång</t>
+          <t>Meåforsbodarna, Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577325.546075945</v>
+        <v>577490</v>
       </c>
       <c r="R3" t="n">
-        <v>7055743.864079177</v>
+        <v>7055743</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,59 +891,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109004574</v>
+        <v>112332566</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Meåforsbodarna, Ång</t>
+          <t>Meåforsbodarna, Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577467.7251708691</v>
+        <v>577488</v>
       </c>
       <c r="R4" t="n">
-        <v>7055722.866542344</v>
+        <v>7055759</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,71 +987,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109007677</v>
+        <v>112333072</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5747</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Meåforsbodarna, Ång</t>
+          <t>Meåforsbodarna, Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577270.2824433909</v>
+        <v>577470</v>
       </c>
       <c r="R5" t="n">
-        <v>7055708.258991051</v>
+        <v>7055718</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,63 +1095,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112332762</v>
+        <v>112332671</v>
       </c>
       <c r="B6" t="n">
-        <v>88221</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Meåforsbodarna (Meåforsbodarna), Ång</t>
+          <t>Meåforsbodarna, Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577465</v>
+        <v>577471</v>
       </c>
       <c r="R6" t="n">
-        <v>7055745</v>
+        <v>7055746</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,27 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112333072</v>
+        <v>112332762</v>
       </c>
       <c r="B7" t="n">
-        <v>89145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,35 +1226,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5747</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Meåforsbodarna (Meåforsbodarna), Ång</t>
+          <t>Meåforsbodarna, Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577470</v>
+        <v>577465</v>
       </c>
       <c r="R7" t="n">
-        <v>7055718</v>
+        <v>7055745</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,27 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112333171</v>
+        <v>109004574</v>
       </c>
       <c r="B8" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,38 +1334,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Meåforsbodarna (Meåforsbodarna), Ång</t>
+          <t>Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577465</v>
+        <v>577468</v>
       </c>
       <c r="R8" t="n">
-        <v>7055745</v>
+        <v>7055723</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,22 +1394,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112333286</v>
+        <v>109004914</v>
       </c>
       <c r="B9" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,38 +1447,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Meåforsbodarna (Meåforsbodarna), Ång</t>
+          <t>Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577520</v>
+        <v>577479</v>
       </c>
       <c r="R9" t="n">
-        <v>7055681</v>
+        <v>7055698</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,22 +1507,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,15 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112332671</v>
+        <v>109007677</v>
       </c>
       <c r="B10" t="n">
-        <v>89155</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,38 +1560,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5754</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Meåforsbodarna (Meåforsbodarna), Ång</t>
+          <t>Meåforsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577471</v>
+        <v>577270</v>
       </c>
       <c r="R10" t="n">
-        <v>7055746</v>
+        <v>7055709</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,22 +1620,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,12 +1650,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,12 +1665,7 @@
         <v>119374249</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,6 +1775,114 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>109005788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Meåforsbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577408</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7055658</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
